--- a/mcap_wise_stock_allocation.xlsx
+++ b/mcap_wise_stock_allocation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anike\Desktop\Ocean_dev\Momentum Handover\Momentum Handover\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Ocean Finvest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3111BF23-F798-4C32-A177-93BADC557FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E2950F-57BB-4B29-86ED-B0EC11EF6AD5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{378BAE51-5B45-4345-B3E6-98211FC13586}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460" xr2:uid="{378BAE51-5B45-4345-B3E6-98211FC13586}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -44,48 +44,21 @@
     <t>MCAP</t>
   </si>
   <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>LARGE CAP</t>
-  </si>
-  <si>
-    <t>BANKINDIA</t>
-  </si>
-  <si>
-    <t>MID CAP</t>
-  </si>
-  <si>
     <t>BHARATFORG</t>
   </si>
   <si>
     <t>BSE</t>
   </si>
   <si>
-    <t>SMALL CAP</t>
-  </si>
-  <si>
     <t>COALINDIA</t>
   </si>
   <si>
-    <t>CUMMINSIND</t>
-  </si>
-  <si>
-    <t>FEDERALBNK</t>
-  </si>
-  <si>
     <t>GESHIP</t>
   </si>
   <si>
     <t>HINDALCO</t>
   </si>
   <si>
-    <t>INDIANB</t>
-  </si>
-  <si>
-    <t>KARURVYSYA</t>
-  </si>
-  <si>
     <t>MAHABANK</t>
   </si>
   <si>
@@ -95,29 +68,56 @@
     <t>NATIONALUM</t>
   </si>
   <si>
-    <t>NAVINFLUOR</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
     <t>TORNTPOWER</t>
   </si>
   <si>
-    <t>UNIONBANK</t>
-  </si>
-  <si>
     <t>VEDL</t>
+  </si>
+  <si>
+    <t>SMALLCAP</t>
+  </si>
+  <si>
+    <t>MIDCAP</t>
+  </si>
+  <si>
+    <t>LARGECAP</t>
+  </si>
+  <si>
+    <t>ACUTAAS</t>
+  </si>
+  <si>
+    <t>BHEL</t>
+  </si>
+  <si>
+    <t>ABB</t>
+  </si>
+  <si>
+    <t>ATHERENERG</t>
+  </si>
+  <si>
+    <t>SAIL</t>
+  </si>
+  <si>
+    <t>GLENMARK</t>
+  </si>
+  <si>
+    <t>IPCALAB</t>
+  </si>
+  <si>
+    <t>GVT&amp;D</t>
+  </si>
+  <si>
+    <t>VTL</t>
+  </si>
+  <si>
+    <t>KIRLOSENG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,13 +483,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB0FD57-3EA9-4368-BBFB-F00FA8EF4B59}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,164 +497,164 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B21" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
